--- a/Cronograma_Proyecto_Bim_2.xlsx
+++ b/Cronograma_Proyecto_Bim_2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salacomputo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92FA668D-6014-41CA-8ED2-0D0547A4CCC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0510E5C7-A2E5-42F9-8E17-77C8F830ABE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
   <si>
     <t>Tarea</t>
   </si>
@@ -131,9 +131,6 @@
   </si>
   <si>
     <t>S7 20-may</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  v</t>
   </si>
 </sst>
 </file>
@@ -530,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
@@ -829,7 +826,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>24</v>
@@ -849,11 +846,6 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
     </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C21" t="s">
-        <v>37</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
